--- a/ExcelProject/ReportTutor.xlsx
+++ b/ExcelProject/ReportTutor.xlsx
@@ -1,146 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="ReportTutor"/>
+    <sheet name="ReportTutor" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="32">
-  <si>
-    <t>Execute</t>
-  </si>
-  <si>
-    <t>TestCase</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>Expected Result</t>
-  </si>
-  <si>
-    <t>Actual Result</t>
-  </si>
-  <si>
-    <t>Result</t>
-  </si>
-  <si>
-    <t>Revise</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>TC10:01</t>
-  </si>
-  <si>
-    <t>ให้ความรู้ได้เป็นอย่างดีเยี่ยมGood888!!!</t>
-  </si>
-  <si>
-    <t>รายงานสำเร็จ</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>TC10:02</t>
-  </si>
-  <si>
-    <t>提供優秀的知識提供優秀的知識提供優秀的知</t>
-  </si>
-  <si>
-    <t>กรุณากรอกเป็นภาษาไทย ภาษาอังกฤษ ตัวเลข [0-9] และอักขระพิเศษ</t>
-  </si>
-  <si>
-    <t>TC10:03</t>
-  </si>
-  <si>
-    <t>โดนติวเตอร์ด่าแรงมาก</t>
-  </si>
-  <si>
-    <t>TC10:04</t>
-  </si>
-  <si>
-    <t>โดนติวเตอร์ด่าแรงมากๆ</t>
-  </si>
-  <si>
-    <t>TC10:05</t>
-  </si>
-  <si>
-    <t>วิชานี้เรียนแล้วไม่ได้อะไรเลยคนสอนมีความเป็นโรคจิตชอบว่าร้ายชอบกล่าวหาคนอื่นโดยไม่ทรายถึงสาเหตุที่แท้จริงไม่ยอมรับผิดแล้วมีความมั่นใจแต่ไม่ยอมรับผิดชอบว่าคนอืนลับหลักชอบเอาเรื่องของคนอื่นมานินทาทั้งๆที่มันไม่ได้เกี่ยวกับการติวสักนิดเดียวอยากให้ปิดคอร์สไป</t>
-  </si>
-  <si>
-    <t>TC10:06</t>
-  </si>
-  <si>
-    <t>วิชานี้เรียนแล้วไม่ได้อะไรเลยคนสอนมีความเป็นโรคจิตชอบว่าร้ายชอบกล่าวหาคนอื่นโดยไม่ทรายถึงสาเหตุที่แท้จริงไม่ยอมรับผิดแล้วมีความมั่นใจแต่ไม่ยอมรับผิดชอบว่าคนอื่นลับหลักชอบเอาเรื่องของคนอื่นมานินทาทั้งๆที่มันไม่ได้เกี่ยวกับการติวสักนิดเดียวอยากให้ปิดคอร์สไป</t>
-  </si>
-  <si>
-    <t>TC10:07</t>
-  </si>
-  <si>
-    <t>หลอกเอาเงินนี่ครับ!</t>
-  </si>
-  <si>
-    <t>กรุณากรอกมีความยาวตั้งแต่ 20 ตัวอักษรขึ้นไป และไม่เกิน 255 ตัวอักษร</t>
-  </si>
-  <si>
-    <t>TC10:08</t>
-  </si>
-  <si>
-    <t>วิชานี้เรียนแล้วไม่ได้อะไรเลยคนสอนมีความเป็นโรคจิตชอบว่าร้ายชอบกล่าวหาคนอื่นโดยไม่ทรายถึงสาเหตุที่แท้จริงไม่ยอมรับผิดแล้วมีความมั่นใจแต่ไม่ยอมรับผิดชอบว่าคนอืนลับหลักชอบเอาเรื่องของคนอื่นมานินทาทั้งๆ ที่มันไม่ได้เกี่ยวกับการติวสักนิดเดียวอยากให้ปิดคอร์สไปซ</t>
-  </si>
-  <si>
-    <t>TC10:09</t>
-  </si>
-  <si>
-    <t>โดนติวเตอร์ด่าแรงมาก ๆ และ ถูกถูกนินทาลับหลัง</t>
-  </si>
-  <si>
-    <t>TC10:10</t>
-  </si>
-  <si>
-    <t>กรุณากรอกข้อมูลสำหรับการรายงาน</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Angsana New"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFff0000"/>
       <name val="Angsana New"/>
       <family val="2"/>
+      <color rgb="FFff0000"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -178,34 +77,99 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -493,212 +457,393 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" style="5" width="9.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="5" width="9.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="5" width="160.14785714285713" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="5" width="41.86214285714286" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="5" width="18.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="5" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="5" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col width="9.147857142857141" bestFit="1" customWidth="1" style="5" min="1" max="1"/>
+    <col width="9.147857142857141" bestFit="1" customWidth="1" style="6" min="2" max="2"/>
+    <col width="162.8621428571429" bestFit="1" customWidth="1" style="6" min="3" max="3"/>
+    <col width="39.86214285714286" bestFit="1" customWidth="1" style="6" min="4" max="4"/>
+    <col width="26.43357142857143" bestFit="1" customWidth="1" style="6" min="5" max="5"/>
+    <col width="14.14785714285714" bestFit="1" customWidth="1" style="6" min="6" max="6"/>
+    <col width="14.14785714285714" bestFit="1" customWidth="1" style="6" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="21.75">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="21.75">
-      <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="22.5">
-      <c r="A3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="21.75">
-      <c r="A4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="21.75">
-      <c r="A5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="21.75">
-      <c r="A6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="21.75">
-      <c r="A7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="21.75">
-      <c r="A8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="21.75">
-      <c r="A9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="21.75">
-      <c r="A10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="22.5">
-      <c r="A11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
+    <row r="1" ht="21" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Execute</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="21" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>TC10:01</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>ให้ความรู้ได้เป็นอย่างดีเยี่ยมGood888!!!</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>รายงานผู้สอนสำเร็จ</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>รายงานผู้สอนสำเร็จ</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>TC10:02</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>提供優秀的知識提供優秀的知識提供優秀的知</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>กรุณากรอกเป็นภาษาไทย ภาษาอังกฤษ ตัวเลข [0-9] และอักขระพิเศษ</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>รายงานผู้สอนสำเร็จ</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="21" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>TC10:03</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>โดนติวเตอร์ด่าแรงมาก</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>รายงานผู้สอนสำเร็จ</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>รายงานผู้สอนสำเร็จ</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21" customHeight="1">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>TC10:04</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>โดนติวเตอร์ด่าแรงมากๆ</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>รายงานผู้สอนสำเร็จ</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>รายงานผู้สอนสำเร็จ</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="21" customHeight="1">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>TC10:05</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>วิชานี้เรียนแล้วไม่ได้อะไรเลยคนสอนมีความเป็นโรคจิตชอบว่าร้ายชอบกล่าวหาคนอื่นโดยไม่ทรายถึงสาเหตุที่แท้จริงไม่ยอมรับผิดแล้วมีความมั่นใจแต่ไม่ยอมรับผิดชอบว่าคนอืนลับหลักชอบเอาเรื่องของคนอื่นมานินทาทั้งๆที่มันไม่ได้เกี่ยวกับการติวสักนิดเดียวอยากให้ปิดคอร์สไป</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>รายงานผู้สอนสำเร็จ</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>ไม่สามารถรายงานได้</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="21" customHeight="1">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>TC10:06</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>วิชานี้เรียนแล้วไม่ได้อะไรเลยคนสอนมีความเป็นโรคจิตชอบว่าร้ายชอบกล่าวหาคนอื่นโดยไม่ทรายถึงสาเหตุที่แท้จริงไม่ยอมรับผิดแล้วมีความมั่นใจแต่ไม่ยอมรับผิดชอบว่าคนอื่นลับหลักชอบเอาเรื่องของคนอื่นมานินทาทั้งๆที่มันไม่ได้เกี่ยวกับการติวสักนิดเดียวอยากให้ปิดคอร์สไป</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>รายงานผู้สอนสำเร็จ</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>ไม่สามารถรายงานได้</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="21" customHeight="1">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>TC10:07</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>หลอกเอาเงินนี่ครับ!</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>รายละเอียดต้องมีความยาว 20-255 ตัวอักษร</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n"/>
+    </row>
+    <row r="9" ht="21" customHeight="1">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>TC10:08</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>วิชานี้เรียนแล้วไม่ได้อะไรเลยคนสอนมีความเป็นโรคจิตชอบว่าร้ายชอบกล่าวหาคนอื่นโดยไม่ทรายถึงสาเหตุที่แท้จริงไม่ยอมรับผิดแล้วมีความมั่นใจแต่ไม่ยอมรับผิดชอบว่าคนอืนลับหลักชอบเอาเรื่องของคนอื่นมานินทาทั้งๆ ที่มันไม่ได้เกี่ยวกับการติวสักนิดเดียวอยากให้ปิดคอร์สไปซ</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>รายละเอียดต้องมีความยาว 20-255 ตัวอักษร</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+    </row>
+    <row r="10" ht="21" customHeight="1">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>TC10:09</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>โดนติวเตอร์ด่าแรงมาก ๆ และ ถูกถูกนินทาลับหลัง</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>รายงานผู้สอนสำเร็จ</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>รายงานผู้สอนสำเร็จ</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="21.75" customHeight="1">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>TC10:10</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>กรุณากรอกข้อมูลสำหรับการรายงาน</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
